--- a/data/trans_orig/P2A_ner_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P2A_ner_R-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>659</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6423</t>
+          <t>5672</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1959</t>
+          <t>1609</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8207</t>
+          <t>8653</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3278</t>
+          <t>3201</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11671</t>
+          <t>11911</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>12,05%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41284</t>
+          <t>42035</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47039</t>
+          <t>47048</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42957</t>
+          <t>42511</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49205</t>
+          <t>49555</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>87200</t>
+          <t>86960</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>95593</t>
+          <t>95670</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,76%</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3791</t>
+          <t>4418</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4229</t>
+          <t>3981</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>642</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5765</t>
+          <t>6205</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>64096</t>
+          <t>63469</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>60705</t>
+          <t>60953</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>127055</t>
+          <t>126615</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>132187</t>
+          <t>132178</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3782</t>
+          <t>3419</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3808</t>
+          <t>3185</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4394</t>
+          <t>5543</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60915</t>
+          <t>61278</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>64094</t>
+          <t>64717</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>128206</t>
+          <t>127057</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4158</t>
+          <t>4239</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5255</t>
+          <t>4771</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>657</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6155</t>
+          <t>7274</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>61896</t>
+          <t>61815</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>68261</t>
+          <t>68745</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>133414</t>
+          <t>132295</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>138910</t>
+          <t>138912</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2895</t>
+          <t>3253</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3173</t>
+          <t>2558</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>12,22%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6646</t>
+          <t>6288</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17768</t>
+          <t>18383</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>4357</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4450</t>
+          <t>3817</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>48552</t>
+          <t>47914</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>94479</t>
+          <t>95112</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4261</t>
+          <t>4926</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>656</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7049</t>
+          <t>6683</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>1398</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8307</t>
+          <t>8329</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>106385</t>
+          <t>105720</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>103737</t>
+          <t>104103</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>110105</t>
+          <t>110130</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>213126</t>
+          <t>213104</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>219462</t>
+          <t>220035</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7640</t>
+          <t>7531</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>982</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6940</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3440</t>
+          <t>3536</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11409</t>
+          <t>11631</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>82527</t>
+          <t>82636</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>88885</t>
+          <t>88926</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>89637</t>
+          <t>90299</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>95605</t>
+          <t>95595</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>175336</t>
+          <t>175114</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>183305</t>
+          <t>183209</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6795</t>
+          <t>6303</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>17334</t>
+          <t>17237</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>8985</t>
+          <t>9182</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>21348</t>
+          <t>20637</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>17985</t>
+          <t>18112</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>34398</t>
+          <t>34993</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>486025</t>
+          <t>486122</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>496564</t>
+          <t>497056</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>507201</t>
+          <t>507912</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>519564</t>
+          <t>519367</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>997510</t>
+          <t>996915</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1013923</t>
+          <t>1013796</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,24%</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3356</t>
+          <t>3631</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>4159</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5528</t>
+          <t>4838</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22001</t>
+          <t>21726</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34078</t>
+          <t>33921</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>57910</t>
+          <t>58600</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>618</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4930</t>
+          <t>5213</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>619</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5157</t>
+          <t>4749</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>49456</t>
+          <t>49173</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>53775</t>
+          <t>53768</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>108115</t>
+          <t>108523</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>112652</t>
+          <t>112653</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>814</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6624</t>
+          <t>7252</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>663</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6201</t>
+          <t>6078</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2716</t>
+          <t>2676</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10845</t>
+          <t>10344</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>43056</t>
+          <t>42428</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>48916</t>
+          <t>48866</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>49271</t>
+          <t>49394</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>54823</t>
+          <t>54809</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>94307</t>
+          <t>94808</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>102436</t>
+          <t>102476</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,46%</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5433,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5978</t>
+          <t>6226</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3506</t>
+          <t>3775</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>721</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6530</t>
+          <t>6809</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12065</t>
+          <t>11817</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>65,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21124</t>
+          <t>20855</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36143</t>
+          <t>35864</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>41957</t>
+          <t>41952</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4975</t>
+          <t>3987</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5055</t>
+          <t>4266</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>39567</t>
+          <t>40555</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>89020</t>
+          <t>89809</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5969,7 +5969,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4421</t>
+          <t>4550</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>645</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5694</t>
+          <t>5457</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1343</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7470</t>
+          <t>7521</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -6227,7 +6227,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>112283</t>
+          <t>112154</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>116083</t>
+          <t>116320</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>121133</t>
+          <t>121132</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>231010</t>
+          <t>230959</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>237137</t>
+          <t>237161</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1376</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7458</t>
+          <t>7736</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4266</t>
+          <t>5658</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>2115</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10025</t>
+          <t>9584</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>108081</t>
+          <t>107803</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>114220</t>
+          <t>114163</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>126202</t>
+          <t>124810</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>235982</t>
+          <t>236423</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>243951</t>
+          <t>243892</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9022</t>
+          <t>8788</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>21847</t>
+          <t>22044</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>3953</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>13079</t>
+          <t>12722</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>14645</t>
+          <t>14501</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>30019</t>
+          <t>30036</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>455118</t>
+          <t>454921</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>467943</t>
+          <t>468177</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>525702</t>
+          <t>526059</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>534764</t>
+          <t>534828</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>985727</t>
+          <t>985710</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1001101</t>
+          <t>1001245</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,57%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2372</t>
+          <t>2239</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8374</t>
+          <t>8884</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>809</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8184</t>
+          <t>7247</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4021</t>
+          <t>4190</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12815</t>
+          <t>12850</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,2%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37012</t>
+          <t>36502</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43014</t>
+          <t>43147</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>43810</t>
+          <t>44747</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51178</t>
+          <t>51185</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>84565</t>
+          <t>84530</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>93359</t>
+          <t>93190</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,7%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>1324</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8274</t>
+          <t>7993</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1887</t>
+          <t>1883</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8462</t>
+          <t>8248</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4112</t>
+          <t>4396</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13176</t>
+          <t>13914</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>62428</t>
+          <t>62709</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>69393</t>
+          <t>69378</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>71533</t>
+          <t>71747</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>78108</t>
+          <t>78112</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>137521</t>
+          <t>136783</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>146585</t>
+          <t>146301</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,08%</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>4321</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1126</t>
+          <t>1405</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7249</t>
+          <t>7907</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1586</t>
+          <t>1544</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9029</t>
+          <t>8918</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54761</t>
+          <t>53792</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58928</t>
+          <t>58270</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>65051</t>
+          <t>64772</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>115260</t>
+          <t>115371</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>122703</t>
+          <t>122745</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1222</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7065</t>
+          <t>7051</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,82 +8423,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>15,63%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>5756</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2367</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>10694</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>12,08%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>4,97%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>22,44%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>9046</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>4862</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>14531</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>9,75%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>5,24%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>15,66%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>5756</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2479</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>10848</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>12,08%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>5,2%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>22,77%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>9046</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>5048</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>15054</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>9,75%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>5,44%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>16,23%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>38048</t>
+          <t>38062</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>43891</t>
+          <t>43872</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,82 +8536,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>84,37%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,25%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>41894</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>36956</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>45283</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>87,92%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>77,56%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>95,03%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>83717</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>78232</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>87901</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>90,25%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>84,34%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,29%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>41894</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>36802</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>45171</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>87,92%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>77,23%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>94,8%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>83717</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>77709</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>87715</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>90,25%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>83,77%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,76%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>669</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6230</t>
+          <t>6154</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>596</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5506</t>
+          <t>5423</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9115</t>
+          <t>9335</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,75%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26145</t>
+          <t>26221</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31690</t>
+          <t>31706</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30010</t>
+          <t>30093</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34921</t>
+          <t>34920</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>58775</t>
+          <t>58555</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>65848</t>
+          <t>65885</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,05%</t>
         </is>
       </c>
     </row>
@@ -9099,7 +9099,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4345</t>
+          <t>4437</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4565</t>
+          <t>4993</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>706</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6869</t>
+          <t>6882</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,74%</t>
         </is>
       </c>
     </row>
@@ -9207,7 +9207,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22938</t>
+          <t>22846</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26791</t>
+          <t>26363</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>51770</t>
+          <t>51757</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>57919</t>
+          <t>57933</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1401</t>
+          <t>1426</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8901</t>
+          <t>9263</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9477,7 +9477,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5720</t>
+          <t>5661</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2729</t>
+          <t>3198</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11515</t>
+          <t>13039</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>107864</t>
+          <t>107502</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>115364</t>
+          <t>115339</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,7 +9585,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>113403</t>
+          <t>113462</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -9600,7 +9600,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>224373</t>
+          <t>222849</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>233159</t>
+          <t>232690</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,64%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2581</t>
+          <t>2542</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10211</t>
+          <t>10203</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9855</t>
+          <t>9171</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9835,7 +9835,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6368</t>
+          <t>6400</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16046</t>
+          <t>16854</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>119442</t>
+          <t>119450</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>127072</t>
+          <t>127111</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>129368</t>
+          <t>130052</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>137221</t>
+          <t>137212</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>252830</t>
+          <t>252022</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>262508</t>
+          <t>262476</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,62%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>18735</t>
+          <t>19551</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>35273</t>
+          <t>35676</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>19518</t>
+          <t>19984</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>36715</t>
+          <t>37235</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>42709</t>
+          <t>41585</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>65880</t>
+          <t>65626</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>490117</t>
+          <t>489714</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>506655</t>
+          <t>505839</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>534318</t>
+          <t>533798</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>551515</t>
+          <t>551049</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1030543</t>
+          <t>1030797</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1053714</t>
+          <t>1054838</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,21%</t>
         </is>
       </c>
     </row>
@@ -10707,7 +10707,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10777,7 +10777,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3644</t>
+          <t>3523</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -10815,7 +10815,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69621</t>
+          <t>69576</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -10830,7 +10830,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -10885,7 +10885,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>149004</t>
+          <t>149125</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -10900,7 +10900,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1960</t>
+          <t>1580</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10938</t>
+          <t>10334</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2592</t>
+          <t>2322</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10053</t>
+          <t>9195</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5696</t>
+          <t>5276</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17235</t>
+          <t>16344</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>116716</t>
+          <t>117320</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>125694</t>
+          <t>126074</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>117543</t>
+          <t>118401</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>125004</t>
+          <t>125274</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>238015</t>
+          <t>238906</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>249554</t>
+          <t>249974</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,93%</t>
         </is>
       </c>
     </row>
@@ -11393,7 +11393,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4776</t>
+          <t>3890</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11408,7 +11408,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1444</t>
+          <t>1485</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7280</t>
+          <t>8257</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>2053</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9348</t>
+          <t>9226</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -11501,7 +11501,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53492</t>
+          <t>54378</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59883</t>
+          <t>58906</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>65719</t>
+          <t>65678</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>116083</t>
+          <t>116205</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>123498</t>
+          <t>123378</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,36%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4902</t>
+          <t>4930</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>166</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4908</t>
+          <t>5140</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>65241</t>
+          <t>65213</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>69970</t>
+          <t>69973</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>143370</t>
+          <t>143138</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>147959</t>
+          <t>148112</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,89%</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2659</t>
+          <t>2855</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2791</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3623</t>
+          <t>4254</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -12187,7 +12187,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31854</t>
+          <t>31658</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -12202,7 +12202,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>37675</t>
+          <t>37928</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -12257,7 +12257,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>71609</t>
+          <t>70978</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -12272,7 +12272,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -12417,7 +12417,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>507</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -12432,7 +12432,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>511</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4445</t>
+          <t>4840</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1646</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7377</t>
+          <t>6880</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -12535,7 +12535,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>45646</t>
+          <t>45660</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12550,7 +12550,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>51741</t>
+          <t>51346</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>55693</t>
+          <t>55675</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>94976</t>
+          <t>95473</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>100707</t>
+          <t>100754</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,44%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>3407</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12215</t>
+          <t>12322</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7045</t>
+          <t>6653</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20603</t>
+          <t>20987</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13078</t>
+          <t>12547</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>28359</t>
+          <t>28303</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>112293</t>
+          <t>112186</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>120583</t>
+          <t>121101</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>135409</t>
+          <t>135025</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>148967</t>
+          <t>149359</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>252161</t>
+          <t>252217</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>267442</t>
+          <t>267973</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,53%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11521</t>
+          <t>11725</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26044</t>
+          <t>25114</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13479</t>
+          <t>13675</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>29234</t>
+          <t>28191</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>29397</t>
+          <t>28933</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>48416</t>
+          <t>49081</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>17,02%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>105575</t>
+          <t>106505</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>120098</t>
+          <t>119894</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>127561</t>
+          <t>128604</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>143316</t>
+          <t>143120</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>239998</t>
+          <t>239333</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>259017</t>
+          <t>259481</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,97%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>26948</t>
+          <t>27771</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>46707</t>
+          <t>47056</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>33070</t>
+          <t>33568</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>55711</t>
+          <t>56348</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>65472</t>
+          <t>65345</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>95484</t>
+          <t>95924</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13536,7 +13536,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>619448</t>
+          <t>619099</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>639207</t>
+          <t>638384</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>706261</t>
+          <t>705624</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>728902</t>
+          <t>728404</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1332643</t>
+          <t>1332203</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1362655</t>
+          <t>1362782</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,7 +13644,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
